--- a/12627677.xlsx
+++ b/12627677.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -119,7 +119,7 @@
     <t>Course / Section:</t>
   </si>
   <si>
-    <t>MCA</t>
+    <t>MCA/D2635</t>
   </si>
   <si>
     <t>Month:</t>
@@ -186,6 +186,33 @@
   </si>
   <si>
     <t>Example row — replace with your own data. Felt a bit tired after evening class.</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Sleep More ,Feeled Relaxedd</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>24O</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>Feeling active by morning after classes feel low</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
   </si>
 </sst>
 </file>
@@ -1058,47 +1085,97 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
+      <c r="A7" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="16">
+        <v>420</v>
+      </c>
+      <c r="C7" s="16">
+        <v>20</v>
+      </c>
+      <c r="D7" s="16">
+        <v>60</v>
+      </c>
+      <c r="E7" s="16">
+        <v>45</v>
+      </c>
+      <c r="F7" s="16">
+        <v>0</v>
+      </c>
+      <c r="G7" s="16">
+        <v>0</v>
+      </c>
+      <c r="H7" s="16">
+        <v>240</v>
+      </c>
       <c r="I7" s="17">
         <f>IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
       </c>
       <c r="J7" s="17">
         <f>IF(I7="","",1440-I7)</f>
       </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="18"/>
+      <c r="K7" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N7" s="18" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
+      <c r="A8" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="16">
+        <v>30</v>
+      </c>
+      <c r="D8" s="16">
+        <v>45</v>
+      </c>
+      <c r="E8" s="16">
+        <v>30</v>
+      </c>
+      <c r="F8" s="16">
+        <v>200</v>
+      </c>
+      <c r="G8" s="16">
+        <v>4</v>
+      </c>
+      <c r="H8" s="16">
+        <v>180</v>
+      </c>
       <c r="I8" s="17">
         <f>IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
       </c>
       <c r="J8" s="17">
         <f>IF(I8="","",1440-I8)</f>
       </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="18"/>
+      <c r="K8" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N8" s="18" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
+      <c r="A9" s="15" t="s">
+        <v>66</v>
+      </c>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>

--- a/12627677.xlsx
+++ b/12627677.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="70">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -134,6 +134,9 @@
     <t>Felling Active in classes but in night feeling low  and underconfident</t>
   </si>
   <si>
+    <t>Trying to figure out what is going on my life</t>
+  </si>
+  <si>
     <t>My Data, My Code</t>
   </si>
   <si>
@@ -231,7 +234,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy/m/d"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,8 +252,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -309,7 +318,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -373,7 +382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -393,40 +402,40 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
@@ -435,7 +444,7 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
@@ -453,9 +462,6 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -468,8 +474,8 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="12" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="13" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -776,22 +782,22 @@
   <dimension ref="A1:A39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="32" width="42.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="26" width="42.14785714285715" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="23.25">
       <c r="A1" s="27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="16.5">
       <c r="A2" s="28" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
@@ -799,12 +805,12 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
@@ -812,22 +818,22 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
@@ -835,17 +841,17 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="30" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
@@ -853,77 +859,77 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="31" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
@@ -931,17 +937,17 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="31" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
@@ -1245,7 +1251,7 @@
         <v>35</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5" customFormat="1" s="12">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="46.5" customFormat="1" s="12">
       <c r="A9" s="19" t="s">
         <v>36</v>
       </c>
@@ -1290,34 +1296,74 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5" customFormat="1" s="12">
-      <c r="A10" s="23"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
+      <c r="A10" s="23">
+        <v>46260.229166666664</v>
+      </c>
+      <c r="B10" s="20">
+        <v>300</v>
+      </c>
+      <c r="C10" s="20">
+        <v>10</v>
+      </c>
+      <c r="D10" s="20">
+        <v>80</v>
+      </c>
+      <c r="E10" s="20">
+        <v>50</v>
+      </c>
+      <c r="F10" s="20">
+        <v>300</v>
+      </c>
+      <c r="G10" s="20">
+        <v>6</v>
+      </c>
+      <c r="H10" s="20">
+        <v>100</v>
+      </c>
       <c r="I10" s="21">
         <f>IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
       </c>
       <c r="J10" s="21">
         <f>IF(I10="","",1440-I10)</f>
       </c>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="22"/>
+      <c r="K10" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" s="22" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5" customFormat="1" s="12">
-      <c r="A11" s="23"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
+      <c r="A11" s="23">
+        <v>46261.229166666664</v>
+      </c>
+      <c r="B11" s="20">
+        <v>240</v>
+      </c>
+      <c r="C11" s="20">
+        <v>20</v>
+      </c>
+      <c r="D11" s="20">
+        <v>120</v>
+      </c>
+      <c r="E11" s="20">
+        <v>50</v>
+      </c>
+      <c r="F11" s="20">
+        <v>300</v>
+      </c>
+      <c r="G11" s="20">
+        <v>6</v>
+      </c>
+      <c r="H11" s="20">
+        <v>60</v>
+      </c>
       <c r="I11" s="21">
         <f>IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
       </c>

--- a/12627677.xlsx
+++ b/12627677.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="71">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t>Trying to figure out what is going on my life</t>
+  </si>
+  <si>
+    <t>Track you time efficiently and manage things</t>
   </si>
   <si>
     <t>My Data, My Code</t>
@@ -787,17 +790,17 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="23.25">
       <c r="A1" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="16.5">
       <c r="A2" s="28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
@@ -805,12 +808,12 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
@@ -818,22 +821,22 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
@@ -841,17 +844,17 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
@@ -859,77 +862,77 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
@@ -937,17 +940,17 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="31" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
@@ -1370,10 +1373,18 @@
       <c r="J11" s="21">
         <f>IF(I11="","",1440-I11)</f>
       </c>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="22"/>
+      <c r="K11" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" s="22" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5" customFormat="1" s="12">
       <c r="A12" s="23"/>

--- a/12627677.xlsx
+++ b/12627677.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="77">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -144,6 +144,18 @@
   </si>
   <si>
     <t>Nothing to note</t>
+  </si>
+  <si>
+    <t>Feel Better after taking nap</t>
+  </si>
+  <si>
+    <t>Thats my bday feel a little bit good</t>
+  </si>
+  <si>
+    <t>Stop Procastination</t>
+  </si>
+  <si>
+    <t>Cut off your distractions</t>
   </si>
   <si>
     <t>My Data, My Code</t>
@@ -805,17 +817,17 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="23.25">
       <c r="A1" s="32" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="16.5">
       <c r="A2" s="33" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="34" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
@@ -823,12 +835,12 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="36" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="35" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
@@ -836,22 +848,22 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="36" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="35" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="35" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="35" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
@@ -859,17 +871,17 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="36" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="35" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="35" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
@@ -877,77 +889,77 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="36" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="35" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="35" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="35" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="35" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="35" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="35" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="35" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="35" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="35" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="35" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="35" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="35" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="35" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="35" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
@@ -955,17 +967,17 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="36" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="35" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="35" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
@@ -1401,7 +1413,7 @@
         <v>40</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5" customFormat="1" s="14">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="33" customFormat="1" s="14">
       <c r="A12" s="23">
         <v>46262</v>
       </c>
@@ -1490,104 +1502,222 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5" customFormat="1" s="14">
-      <c r="A14" s="23"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
+      <c r="A14" s="23">
+        <v>46264</v>
+      </c>
+      <c r="B14" s="24">
+        <v>480</v>
+      </c>
+      <c r="C14" s="24">
+        <v>0</v>
+      </c>
+      <c r="D14" s="24">
+        <v>60</v>
+      </c>
+      <c r="E14" s="24">
+        <v>100</v>
+      </c>
+      <c r="F14" s="24">
+        <v>0</v>
+      </c>
+      <c r="G14" s="24">
+        <v>0</v>
+      </c>
+      <c r="H14" s="24">
+        <v>300</v>
+      </c>
       <c r="I14" s="25">
         <f>IF(SUM(B14:F14,H14)=0,"",SUM(B14:F14,H14))</f>
       </c>
       <c r="J14" s="25">
         <f>IF(I14="","",1440-I14)</f>
       </c>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="27"/>
+      <c r="K14" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="N14" s="27" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5" customFormat="1" s="14">
-      <c r="A15" s="23"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
+      <c r="A15" s="23">
+        <v>46265</v>
+      </c>
+      <c r="B15" s="24">
+        <v>400</v>
+      </c>
+      <c r="C15" s="24">
+        <v>0</v>
+      </c>
+      <c r="D15" s="24">
+        <v>0</v>
+      </c>
+      <c r="E15" s="24">
+        <v>0</v>
+      </c>
+      <c r="F15" s="24">
+        <v>0</v>
+      </c>
+      <c r="G15" s="24">
+        <v>0</v>
+      </c>
+      <c r="H15" s="24">
+        <v>400</v>
+      </c>
       <c r="I15" s="25">
         <f>IF(SUM(B15:F15,H15)=0,"",SUM(B15:F15,H15))</f>
       </c>
       <c r="J15" s="25">
         <f>IF(I15="","",1440-I15)</f>
       </c>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="27"/>
+      <c r="K15" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" s="27" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5" customFormat="1" s="14">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
+      <c r="A16" s="23">
+        <v>46266</v>
+      </c>
+      <c r="B16" s="24">
+        <v>300</v>
+      </c>
+      <c r="C16" s="24">
+        <v>0</v>
+      </c>
+      <c r="D16" s="24">
+        <v>80</v>
+      </c>
+      <c r="E16" s="24">
+        <v>50</v>
+      </c>
+      <c r="F16" s="24">
+        <v>200</v>
+      </c>
+      <c r="G16" s="24">
+        <v>5</v>
+      </c>
+      <c r="H16" s="24">
+        <v>100</v>
+      </c>
       <c r="I16" s="25">
         <f>IF(SUM(B16:F16,H16)=0,"",SUM(B16:F16,H16))</f>
       </c>
       <c r="J16" s="25">
         <f>IF(I16="","",1440-I16)</f>
       </c>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="26"/>
+      <c r="K16" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" s="26" t="s">
+        <v>26</v>
+      </c>
       <c r="N16" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5" customFormat="1" s="14">
-      <c r="A17" s="23"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
+      <c r="A17" s="23">
+        <v>46267</v>
+      </c>
+      <c r="B17" s="24">
+        <v>300</v>
+      </c>
+      <c r="C17" s="24">
+        <v>30</v>
+      </c>
+      <c r="D17" s="24">
+        <v>45</v>
+      </c>
+      <c r="E17" s="24">
+        <v>30</v>
+      </c>
+      <c r="F17" s="24">
+        <v>200</v>
+      </c>
+      <c r="G17" s="24">
+        <v>5</v>
+      </c>
+      <c r="H17" s="24">
+        <v>60</v>
+      </c>
       <c r="I17" s="25">
         <f>IF(SUM(B17:F17,H17)=0,"",SUM(B17:F17,H17))</f>
       </c>
       <c r="J17" s="25">
         <f>IF(I17="","",1440-I17)</f>
       </c>
-      <c r="K17" s="26"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="26"/>
-      <c r="N17" s="27"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
+      <c r="K17" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M17" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="N17" s="27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5" customFormat="1" s="14">
+      <c r="A18" s="23">
+        <v>-619935.0003240741</v>
+      </c>
+      <c r="B18" s="24">
+        <v>200</v>
+      </c>
+      <c r="C18" s="24">
+        <v>0</v>
+      </c>
+      <c r="D18" s="24">
+        <v>30</v>
+      </c>
+      <c r="E18" s="24">
+        <v>30</v>
+      </c>
+      <c r="F18" s="24">
+        <v>240</v>
+      </c>
+      <c r="G18" s="24">
+        <v>6</v>
+      </c>
+      <c r="H18" s="24">
+        <v>180</v>
+      </c>
       <c r="I18" s="25">
         <f>IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
       </c>
       <c r="J18" s="25">
         <f>IF(I18="","",1440-I18)</f>
       </c>
-      <c r="K18" s="26"/>
-      <c r="L18" s="26"/>
-      <c r="M18" s="26"/>
-      <c r="N18" s="27"/>
+      <c r="K18" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="L18" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="M18" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="N18" s="27" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75" customFormat="1" s="14">
       <c r="A19" s="23"/>

--- a/12627677.xlsx
+++ b/12627677.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="90">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -156,6 +156,45 @@
   </si>
   <si>
     <t>Cut off your distractions</t>
+  </si>
+  <si>
+    <t>Doing Good</t>
+  </si>
+  <si>
+    <t>Satified</t>
+  </si>
+  <si>
+    <t>Good start of the week</t>
+  </si>
+  <si>
+    <t>Work On Focus</t>
+  </si>
+  <si>
+    <t>Completed C++</t>
+  </si>
+  <si>
+    <t>Learn DSA Practically</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>Logic Building</t>
+  </si>
+  <si>
+    <t>Aptitude</t>
+  </si>
+  <si>
+    <t>Learn DBMS</t>
+  </si>
+  <si>
+    <t>Practice SQL Query</t>
+  </si>
+  <si>
+    <t>DSA Striver sheet</t>
   </si>
   <si>
     <t>My Data, My Code</t>
@@ -817,17 +856,17 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="23.25">
       <c r="A1" s="32" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="16.5">
       <c r="A2" s="33" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="34" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
@@ -835,12 +874,12 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="36" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="35" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
@@ -848,22 +887,22 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="36" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="35" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="35" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="35" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
@@ -871,17 +910,17 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="36" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="35" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="35" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
@@ -889,77 +928,77 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="36" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="35" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="35" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="35" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="35" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="35" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="35" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="35" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="35" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="35" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="35" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="35" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="35" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="35" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="35" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
@@ -967,17 +1006,17 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="36" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="35" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="35" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
@@ -1545,7 +1584,7 @@
         <v>43</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5" customFormat="1" s="14">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="33" customFormat="1" s="14">
       <c r="A15" s="23">
         <v>46265</v>
       </c>
@@ -1677,7 +1716,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5" customFormat="1" s="14">
       <c r="A18" s="23">
-        <v>-619935.0003240741</v>
+        <v>46268</v>
       </c>
       <c r="B18" s="24">
         <v>200</v>
@@ -1719,328 +1758,714 @@
         <v>46</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A19" s="23"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5" customFormat="1" s="14">
+      <c r="A19" s="23">
+        <v>46269</v>
+      </c>
+      <c r="B19" s="24">
+        <v>400</v>
+      </c>
+      <c r="C19" s="24">
+        <v>0</v>
+      </c>
+      <c r="D19" s="24">
+        <v>60</v>
+      </c>
+      <c r="E19" s="24">
+        <v>120</v>
+      </c>
+      <c r="F19" s="24">
+        <v>350</v>
+      </c>
+      <c r="G19" s="24">
+        <v>7</v>
+      </c>
+      <c r="H19" s="24">
+        <v>350</v>
+      </c>
       <c r="I19" s="25">
         <f>IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
       </c>
       <c r="J19" s="25">
         <f>IF(I19="","",1440-I19)</f>
       </c>
-      <c r="K19" s="26"/>
-      <c r="L19" s="26"/>
-      <c r="M19" s="26"/>
-      <c r="N19" s="27"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A20" s="23"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
+      <c r="K19" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M19" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="N19" s="27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5" customFormat="1" s="14">
+      <c r="A20" s="23">
+        <v>46270</v>
+      </c>
+      <c r="B20" s="24">
+        <v>450</v>
+      </c>
+      <c r="C20" s="24">
+        <v>0</v>
+      </c>
+      <c r="D20" s="24">
+        <v>70</v>
+      </c>
+      <c r="E20" s="24">
+        <v>100</v>
+      </c>
+      <c r="F20" s="24">
+        <v>0</v>
+      </c>
+      <c r="G20" s="24">
+        <v>0</v>
+      </c>
+      <c r="H20" s="24">
+        <v>300</v>
+      </c>
       <c r="I20" s="25">
         <f>IF(SUM(B20:F20,H20)=0,"",SUM(B20:F20,H20))</f>
       </c>
       <c r="J20" s="25">
         <f>IF(I20="","",1440-I20)</f>
       </c>
-      <c r="K20" s="26"/>
-      <c r="L20" s="26"/>
-      <c r="M20" s="26"/>
-      <c r="N20" s="27"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A21" s="23"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
+      <c r="K20" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M20" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="N20" s="27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5" customFormat="1" s="14">
+      <c r="A21" s="23">
+        <v>46271</v>
+      </c>
+      <c r="B21" s="24">
+        <v>400</v>
+      </c>
+      <c r="C21" s="24">
+        <v>10</v>
+      </c>
+      <c r="D21" s="24">
+        <v>100</v>
+      </c>
+      <c r="E21" s="24">
+        <v>120</v>
+      </c>
+      <c r="F21" s="24">
+        <v>0</v>
+      </c>
+      <c r="G21" s="24">
+        <v>0</v>
+      </c>
+      <c r="H21" s="24">
+        <v>200</v>
+      </c>
       <c r="I21" s="25">
         <f>IF(SUM(B21:F21,H21)=0,"",SUM(B21:F21,H21))</f>
       </c>
       <c r="J21" s="25">
         <f>IF(I21="","",1440-I21)</f>
       </c>
-      <c r="K21" s="26"/>
-      <c r="L21" s="26"/>
-      <c r="M21" s="26"/>
-      <c r="N21" s="27"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A22" s="23"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
+      <c r="K21" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="L21" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="M21" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="N21" s="27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5" customFormat="1" s="14">
+      <c r="A22" s="23">
+        <v>46272</v>
+      </c>
+      <c r="B22" s="24">
+        <v>300</v>
+      </c>
+      <c r="C22" s="24">
+        <v>60</v>
+      </c>
+      <c r="D22" s="24">
+        <v>100</v>
+      </c>
+      <c r="E22" s="24">
+        <v>220</v>
+      </c>
+      <c r="F22" s="24">
+        <v>200</v>
+      </c>
+      <c r="G22" s="24">
+        <v>4</v>
+      </c>
+      <c r="H22" s="24">
+        <v>100</v>
+      </c>
       <c r="I22" s="25">
         <f>IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
       </c>
       <c r="J22" s="25">
         <f>IF(I22="","",1440-I22)</f>
       </c>
-      <c r="K22" s="26"/>
-      <c r="L22" s="26"/>
-      <c r="M22" s="26"/>
-      <c r="N22" s="27"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A23" s="23"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
+      <c r="K22" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M22" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="N22" s="27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5" customFormat="1" s="14">
+      <c r="A23" s="23">
+        <v>46273</v>
+      </c>
+      <c r="B23" s="24">
+        <v>350</v>
+      </c>
+      <c r="C23" s="24">
+        <v>50</v>
+      </c>
+      <c r="D23" s="24">
+        <v>80</v>
+      </c>
+      <c r="E23" s="24">
+        <v>100</v>
+      </c>
+      <c r="F23" s="24">
+        <v>250</v>
+      </c>
+      <c r="G23" s="24">
+        <v>5</v>
+      </c>
+      <c r="H23" s="24">
+        <v>100</v>
+      </c>
       <c r="I23" s="25">
         <f>IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
       </c>
       <c r="J23" s="25">
         <f>IF(I23="","",1440-I23)</f>
       </c>
-      <c r="K23" s="26"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="27"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A24" s="23"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
+      <c r="K23" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M23" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="N23" s="27" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5" customFormat="1" s="14">
+      <c r="A24" s="23">
+        <v>46274</v>
+      </c>
+      <c r="B24" s="24">
+        <v>400</v>
+      </c>
+      <c r="C24" s="24">
+        <v>50</v>
+      </c>
+      <c r="D24" s="24">
+        <v>70</v>
+      </c>
+      <c r="E24" s="24">
+        <v>110</v>
+      </c>
+      <c r="F24" s="24">
+        <v>250</v>
+      </c>
+      <c r="G24" s="24">
+        <v>5</v>
+      </c>
+      <c r="H24" s="24">
+        <v>80</v>
+      </c>
       <c r="I24" s="25">
         <f>IF(SUM(B24:F24,H24)=0,"",SUM(B24:F24,H24))</f>
       </c>
       <c r="J24" s="25">
         <f>IF(I24="","",1440-I24)</f>
       </c>
-      <c r="K24" s="26"/>
-      <c r="L24" s="26"/>
-      <c r="M24" s="26"/>
-      <c r="N24" s="27"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A25" s="23"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
+      <c r="K24" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M24" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="N24" s="27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5" customFormat="1" s="14">
+      <c r="A25" s="23">
+        <v>46275</v>
+      </c>
+      <c r="B25" s="24">
+        <v>400</v>
+      </c>
+      <c r="C25" s="24">
+        <v>60</v>
+      </c>
+      <c r="D25" s="24">
+        <v>90</v>
+      </c>
+      <c r="E25" s="24">
+        <v>100</v>
+      </c>
+      <c r="F25" s="24">
+        <v>300</v>
+      </c>
+      <c r="G25" s="24">
+        <v>6</v>
+      </c>
+      <c r="H25" s="24">
+        <v>100</v>
+      </c>
       <c r="I25" s="25">
         <f>IF(SUM(B25:F25,H25)=0,"",SUM(B25:F25,H25))</f>
       </c>
       <c r="J25" s="25">
         <f>IF(I25="","",1440-I25)</f>
       </c>
-      <c r="K25" s="26"/>
-      <c r="L25" s="26"/>
-      <c r="M25" s="26"/>
-      <c r="N25" s="27"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A26" s="23"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
+      <c r="K25" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="L25" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="M25" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="N25" s="27" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5" customFormat="1" s="14">
+      <c r="A26" s="23">
+        <v>46276</v>
+      </c>
+      <c r="B26" s="24">
+        <v>300</v>
+      </c>
+      <c r="C26" s="24">
+        <v>60</v>
+      </c>
+      <c r="D26" s="24">
+        <v>100</v>
+      </c>
+      <c r="E26" s="24">
+        <v>100</v>
+      </c>
+      <c r="F26" s="24">
+        <v>350</v>
+      </c>
+      <c r="G26" s="24">
+        <v>7</v>
+      </c>
+      <c r="H26" s="24">
+        <v>120</v>
+      </c>
       <c r="I26" s="25">
         <f>IF(SUM(B26:F26,H26)=0,"",SUM(B26:F26,H26))</f>
       </c>
       <c r="J26" s="25">
         <f>IF(I26="","",1440-I26)</f>
       </c>
-      <c r="K26" s="26"/>
-      <c r="L26" s="26"/>
-      <c r="M26" s="26"/>
-      <c r="N26" s="27"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A27" s="23"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
+      <c r="K26" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M26" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="N26" s="27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5" customFormat="1" s="14">
+      <c r="A27" s="23">
+        <v>46277</v>
+      </c>
+      <c r="B27" s="24">
+        <v>400</v>
+      </c>
+      <c r="C27" s="24">
+        <v>60</v>
+      </c>
+      <c r="D27" s="24">
+        <v>90</v>
+      </c>
+      <c r="E27" s="24">
+        <v>100</v>
+      </c>
+      <c r="F27" s="24">
+        <v>0</v>
+      </c>
+      <c r="G27" s="24">
+        <v>0</v>
+      </c>
+      <c r="H27" s="24">
+        <v>200</v>
+      </c>
       <c r="I27" s="25">
         <f>IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
       </c>
       <c r="J27" s="25">
         <f>IF(I27="","",1440-I27)</f>
       </c>
-      <c r="K27" s="26"/>
-      <c r="L27" s="26"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="27"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A28" s="23"/>
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
+      <c r="K27" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="L27" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M27" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="N27" s="27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5" customFormat="1" s="14">
+      <c r="A28" s="23">
+        <v>46278</v>
+      </c>
+      <c r="B28" s="24">
+        <v>400</v>
+      </c>
+      <c r="C28" s="24">
+        <v>20</v>
+      </c>
+      <c r="D28" s="24">
+        <v>80</v>
+      </c>
+      <c r="E28" s="24">
+        <v>120</v>
+      </c>
+      <c r="F28" s="24">
+        <v>0</v>
+      </c>
+      <c r="G28" s="24">
+        <v>0</v>
+      </c>
+      <c r="H28" s="24">
+        <v>200</v>
+      </c>
       <c r="I28" s="25">
         <f>IF(SUM(B28:F28,H28)=0,"",SUM(B28:F28,H28))</f>
       </c>
       <c r="J28" s="25">
         <f>IF(I28="","",1440-I28)</f>
       </c>
-      <c r="K28" s="26"/>
-      <c r="L28" s="26"/>
-      <c r="M28" s="26"/>
-      <c r="N28" s="27"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A29" s="23"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
+      <c r="K28" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="L28" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="M28" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="N28" s="27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5" customFormat="1" s="14">
+      <c r="A29" s="23">
+        <v>46279</v>
+      </c>
+      <c r="B29" s="24">
+        <v>350</v>
+      </c>
+      <c r="C29" s="24">
+        <v>60</v>
+      </c>
+      <c r="D29" s="24">
+        <v>90</v>
+      </c>
+      <c r="E29" s="24">
+        <v>200</v>
+      </c>
+      <c r="F29" s="24">
+        <v>200</v>
+      </c>
+      <c r="G29" s="24">
+        <v>4</v>
+      </c>
+      <c r="H29" s="24">
+        <v>120</v>
+      </c>
       <c r="I29" s="25">
         <f>IF(SUM(B29:F29,H29)=0,"",SUM(B29:F29,H29))</f>
       </c>
       <c r="J29" s="25">
         <f>IF(I29="","",1440-I29)</f>
       </c>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="27"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A30" s="23"/>
-      <c r="B30" s="24"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
+      <c r="K29" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M29" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="N29" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5" customFormat="1" s="14">
+      <c r="A30" s="23">
+        <v>46280</v>
+      </c>
+      <c r="B30" s="24">
+        <v>300</v>
+      </c>
+      <c r="C30" s="24">
+        <v>60</v>
+      </c>
+      <c r="D30" s="24">
+        <v>100</v>
+      </c>
+      <c r="E30" s="24">
+        <v>100</v>
+      </c>
+      <c r="F30" s="24">
+        <v>250</v>
+      </c>
+      <c r="G30" s="24">
+        <v>5</v>
+      </c>
+      <c r="H30" s="24">
+        <v>100</v>
+      </c>
       <c r="I30" s="25">
         <f>IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
       </c>
       <c r="J30" s="25">
         <f>IF(I30="","",1440-I30)</f>
       </c>
-      <c r="K30" s="26"/>
-      <c r="L30" s="26"/>
-      <c r="M30" s="26"/>
-      <c r="N30" s="27"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A31" s="23"/>
-      <c r="B31" s="24"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
+      <c r="K30" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="L30" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M30" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="N30" s="27" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5" customFormat="1" s="14">
+      <c r="A31" s="23">
+        <v>46281</v>
+      </c>
+      <c r="B31" s="24">
+        <v>300</v>
+      </c>
+      <c r="C31" s="24">
+        <v>60</v>
+      </c>
+      <c r="D31" s="24">
+        <v>120</v>
+      </c>
+      <c r="E31" s="24">
+        <v>100</v>
+      </c>
+      <c r="F31" s="24">
+        <v>250</v>
+      </c>
+      <c r="G31" s="24">
+        <v>5</v>
+      </c>
+      <c r="H31" s="24">
+        <v>100</v>
+      </c>
       <c r="I31" s="25">
         <f>IF(SUM(B31:F31,H31)=0,"",SUM(B31:F31,H31))</f>
       </c>
       <c r="J31" s="25">
         <f>IF(I31="","",1440-I31)</f>
       </c>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
-      <c r="M31" s="26"/>
-      <c r="N31" s="27"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A32" s="23"/>
-      <c r="B32" s="24"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
+      <c r="K31" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="M31" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="N31" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5" customFormat="1" s="14">
+      <c r="A32" s="23">
+        <v>46282</v>
+      </c>
+      <c r="B32" s="24">
+        <v>400</v>
+      </c>
+      <c r="C32" s="24">
+        <v>60</v>
+      </c>
+      <c r="D32" s="24">
+        <v>100</v>
+      </c>
+      <c r="E32" s="24">
+        <v>90</v>
+      </c>
+      <c r="F32" s="24">
+        <v>300</v>
+      </c>
+      <c r="G32" s="24">
+        <v>6</v>
+      </c>
+      <c r="H32" s="24">
+        <v>100</v>
+      </c>
       <c r="I32" s="25">
         <f>IF(SUM(B32:F32,H32)=0,"",SUM(B32:F32,H32))</f>
       </c>
       <c r="J32" s="25">
         <f>IF(I32="","",1440-I32)</f>
       </c>
-      <c r="K32" s="26"/>
-      <c r="L32" s="26"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="27"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A33" s="23"/>
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="24"/>
+      <c r="K32" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M32" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="N32" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5" customFormat="1" s="14">
+      <c r="A33" s="23">
+        <v>46283</v>
+      </c>
+      <c r="B33" s="24">
+        <v>350</v>
+      </c>
+      <c r="C33" s="24">
+        <v>60</v>
+      </c>
+      <c r="D33" s="24">
+        <v>90</v>
+      </c>
+      <c r="E33" s="24">
+        <v>120</v>
+      </c>
+      <c r="F33" s="24">
+        <v>350</v>
+      </c>
+      <c r="G33" s="24">
+        <v>7</v>
+      </c>
+      <c r="H33" s="24">
+        <v>120</v>
+      </c>
       <c r="I33" s="25">
         <f>IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
       </c>
       <c r="J33" s="25">
         <f>IF(I33="","",1440-I33)</f>
       </c>
-      <c r="K33" s="26"/>
-      <c r="L33" s="26"/>
-      <c r="M33" s="26"/>
-      <c r="N33" s="27"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A34" s="23"/>
-      <c r="B34" s="24"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="24"/>
+      <c r="K33" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="L33" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="M33" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="N33" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5" customFormat="1" s="14">
+      <c r="A34" s="23">
+        <v>46284</v>
+      </c>
+      <c r="B34" s="24">
+        <v>300</v>
+      </c>
+      <c r="C34" s="24">
+        <v>60</v>
+      </c>
+      <c r="D34" s="24">
+        <v>220</v>
+      </c>
+      <c r="E34" s="24">
+        <v>100</v>
+      </c>
+      <c r="F34" s="24">
+        <v>50</v>
+      </c>
+      <c r="G34" s="24">
+        <v>1</v>
+      </c>
+      <c r="H34" s="24">
+        <v>220</v>
+      </c>
       <c r="I34" s="25">
         <f>IF(SUM(B34:F34,H34)=0,"",SUM(B34:F34,H34))</f>
       </c>
       <c r="J34" s="25">
         <f>IF(I34="","",1440-I34)</f>
       </c>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="27"/>
+      <c r="K34" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="L34" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M34" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="N34" s="27" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A35" s="23"/>
+      <c r="A35" s="23">
+        <v>46285</v>
+      </c>
       <c r="B35" s="24"/>
       <c r="C35" s="24"/>
       <c r="D35" s="24"/>
@@ -2060,7 +2485,9 @@
       <c r="N35" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A36" s="23"/>
+      <c r="A36" s="23">
+        <v>46286</v>
+      </c>
       <c r="B36" s="24"/>
       <c r="C36" s="24"/>
       <c r="D36" s="24"/>
@@ -2080,7 +2507,9 @@
       <c r="N36" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A37" s="23"/>
+      <c r="A37" s="23">
+        <v>46287</v>
+      </c>
       <c r="B37" s="24"/>
       <c r="C37" s="24"/>
       <c r="D37" s="24"/>
@@ -2100,7 +2529,9 @@
       <c r="N37" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A38" s="23"/>
+      <c r="A38" s="23">
+        <v>46288</v>
+      </c>
       <c r="B38" s="24"/>
       <c r="C38" s="24"/>
       <c r="D38" s="24"/>
@@ -2120,7 +2551,9 @@
       <c r="N38" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A39" s="23"/>
+      <c r="A39" s="23">
+        <v>46289</v>
+      </c>
       <c r="B39" s="24"/>
       <c r="C39" s="24"/>
       <c r="D39" s="24"/>
@@ -2140,7 +2573,9 @@
       <c r="N39" s="27"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75" customFormat="1" s="14">
-      <c r="A40" s="23"/>
+      <c r="A40" s="23">
+        <v>46290</v>
+      </c>
       <c r="B40" s="24"/>
       <c r="C40" s="24"/>
       <c r="D40" s="24"/>

--- a/12627677.xlsx
+++ b/12627677.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -195,6 +195,12 @@
   </si>
   <si>
     <t>DSA Striver sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSA </t>
+  </si>
+  <si>
+    <t>Focus on Midterm</t>
   </si>
   <si>
     <t>My Data, My Code</t>
@@ -856,17 +862,17 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="23.25">
       <c r="A1" s="32" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="16.5">
       <c r="A2" s="33" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="34" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
@@ -874,12 +880,12 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="36" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="35" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
@@ -887,22 +893,22 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="36" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="35" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="35" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="35" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
@@ -910,17 +916,17 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="36" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="35" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="35" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
@@ -928,77 +934,77 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="36" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="35" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="35" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="35" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="35" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="35" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="35" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="35" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="35" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="35" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="35" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="35" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
@@ -1006,17 +1012,17 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="36" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="35" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="35" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
@@ -2462,51 +2468,95 @@
         <v>56</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75" customFormat="1" s="14">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5" customFormat="1" s="14">
       <c r="A35" s="23">
         <v>46285</v>
       </c>
-      <c r="B35" s="24"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
+      <c r="B35" s="24">
+        <v>450</v>
+      </c>
+      <c r="C35" s="24">
+        <v>30</v>
+      </c>
+      <c r="D35" s="24">
+        <v>300</v>
+      </c>
+      <c r="E35" s="24">
+        <v>120</v>
+      </c>
+      <c r="F35" s="24">
+        <v>0</v>
+      </c>
+      <c r="G35" s="24">
+        <v>0</v>
+      </c>
+      <c r="H35" s="24">
+        <v>200</v>
+      </c>
       <c r="I35" s="25">
         <f>IF(SUM(B35:F35,H35)=0,"",SUM(B35:F35,H35))</f>
       </c>
       <c r="J35" s="25">
         <f>IF(I35="","",1440-I35)</f>
       </c>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-      <c r="M35" s="26"/>
-      <c r="N35" s="27"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75" customFormat="1" s="14">
+      <c r="K35" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="M35" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="N35" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5" customFormat="1" s="14">
       <c r="A36" s="23">
         <v>46286</v>
       </c>
-      <c r="B36" s="24"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="24"/>
+      <c r="B36" s="24">
+        <v>300</v>
+      </c>
+      <c r="C36" s="24">
+        <v>45</v>
+      </c>
+      <c r="D36" s="24">
+        <v>200</v>
+      </c>
+      <c r="E36" s="24">
+        <v>100</v>
+      </c>
+      <c r="F36" s="24">
+        <v>200</v>
+      </c>
+      <c r="G36" s="24">
+        <v>4</v>
+      </c>
+      <c r="H36" s="24">
+        <v>300</v>
+      </c>
       <c r="I36" s="25">
         <f>IF(SUM(B36:F36,H36)=0,"",SUM(B36:F36,H36))</f>
       </c>
       <c r="J36" s="25">
         <f>IF(I36="","",1440-I36)</f>
       </c>
-      <c r="K36" s="26"/>
-      <c r="L36" s="26"/>
-      <c r="M36" s="26"/>
-      <c r="N36" s="27"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75" customFormat="1" s="14">
+      <c r="K36" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="M36" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="N36" s="27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5" customFormat="1" s="14">
       <c r="A37" s="23">
         <v>46287</v>
       </c>
